--- a/exports/INDUSINDBK_full_report.xlsx
+++ b/exports/INDUSINDBK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.03</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>900.95</v>
+        <v>892.45</v>
       </c>
       <c r="I2" t="n">
         <v>896.4026730249999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.21</v>
+        <v>-3.14</v>
       </c>
       <c r="L2" t="n">
-        <v>2.79</v>
+        <v>4.03</v>
       </c>
       <c r="M2" t="n">
         <v>0.77</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>5.45</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.55208333334</v>
+        <v>44589.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>892.85</v>
+        <v>921.4</v>
       </c>
       <c r="I3" t="n">
         <v>900.4696678617772</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.04</v>
+        <v>-3.24</v>
       </c>
       <c r="L3" t="n">
-        <v>1.27</v>
+        <v>3.71</v>
       </c>
       <c r="M3" t="n">
-        <v>0.22</v>
+        <v>0.46</v>
       </c>
       <c r="N3" t="n">
         <v>3.66</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.93</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44615.55208333334</v>
+        <v>44616.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>948.65</v>
+        <v>896.4</v>
       </c>
       <c r="I4" t="n">
         <v>921.3215763866386</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K4" t="n">
-        <v>2.96</v>
+        <v>-2.71</v>
       </c>
       <c r="L4" t="n">
         <v>5.94</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="N4" t="n">
-        <v>4.06</v>
+        <v>8.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.22</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>879.3</v>
+        <v>916.55</v>
       </c>
       <c r="I5" t="n">
         <v>911.8290156875362</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>1.91</v>
+        <v>-2.25</v>
       </c>
       <c r="L5" t="n">
         <v>4.05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.26</v>
+        <v>3.47</v>
       </c>
       <c r="N5" t="n">
         <v>6.51</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.27</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44685.55208333334</v>
+        <v>44686.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>984.7</v>
+        <v>956.55</v>
       </c>
       <c r="I6" t="n">
         <v>960.5471202883285</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K6" t="n">
-        <v>7.44</v>
+        <v>4.36</v>
       </c>
       <c r="L6" t="n">
         <v>3.16</v>
@@ -783,7 +854,7 @@
         <v>1.56</v>
       </c>
       <c r="N6" t="n">
-        <v>3.12</v>
+        <v>4.74</v>
       </c>
       <c r="O6" t="n">
         <v>2.7</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.82</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>926</v>
+        <v>936.65</v>
       </c>
       <c r="I7" t="n">
         <v>933.6743144699009</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.19</v>
+        <v>2.08</v>
       </c>
       <c r="L7" t="n">
         <v>4.02</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>6.08</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>923.1</v>
+        <v>866.5</v>
       </c>
       <c r="I8" t="n">
         <v>891.1491019383501</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.45</v>
+        <v>-7.49</v>
       </c>
       <c r="L8" t="n">
-        <v>3.55</v>
+        <v>7.92</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>3.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.81</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
         <v>0.97</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.56</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44748.55208333334</v>
+        <v>44749.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>838</v>
+        <v>855.4</v>
       </c>
       <c r="I9" t="n">
         <v>839.406047464309</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K9" t="n">
-        <v>3.29</v>
+        <v>1.28</v>
       </c>
       <c r="L9" t="n">
         <v>3.9</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.62</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1060.3</v>
+        <v>1055.1</v>
       </c>
       <c r="I10" t="n">
         <v>1055.420772592701</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K10" t="n">
-        <v>23.95</v>
+        <v>23.35</v>
       </c>
       <c r="L10" t="n">
         <v>7.68</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>5.18</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44797.38541666666</v>
+        <v>44797.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>1086.7</v>
+        <v>1102</v>
       </c>
       <c r="I11" t="n">
         <v>1100.965766991736</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.99</v>
+        <v>-4.45</v>
       </c>
       <c r="L11" t="n">
-        <v>4.04</v>
+        <v>4.72</v>
       </c>
       <c r="M11" t="n">
         <v>0.15</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.91</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1215</v>
+        <v>1180.2</v>
       </c>
       <c r="I12" t="n">
         <v>1184.201168867243</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>10.25</v>
+        <v>7.1</v>
       </c>
       <c r="L12" t="n">
         <v>5.52</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.33</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44887.38541666666</v>
+        <v>44887.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>1165.85</v>
+        <v>1172.45</v>
       </c>
       <c r="I13" t="n">
         <v>1171.214930706305</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>1.22</v>
+        <v>0.66</v>
       </c>
       <c r="L13" t="n">
         <v>4.58</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.52</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1219.5</v>
+        <v>1201.15</v>
       </c>
       <c r="I14" t="n">
         <v>1203.526947923113</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K14" t="n">
-        <v>4.01</v>
+        <v>2.45</v>
       </c>
       <c r="L14" t="n">
         <v>0.95</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>5.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44924.38541666666</v>
+        <v>44924.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1217.1</v>
+        <v>1225.6</v>
       </c>
       <c r="I15" t="n">
         <v>1222.461292295683</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.33</v>
+        <v>-2.04</v>
       </c>
       <c r="L15" t="n">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="M15" t="n">
         <v>0.64</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>5.42</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1213</v>
+        <v>1182</v>
       </c>
       <c r="I16" t="n">
         <v>1183.505177512948</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.03</v>
+        <v>-3.56</v>
       </c>
       <c r="L16" t="n">
-        <v>4.04</v>
+        <v>4.37</v>
       </c>
       <c r="M16" t="n">
         <v>0.53</v>
       </c>
       <c r="N16" t="n">
-        <v>2.72</v>
+        <v>4.32</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.58</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44966.38541666666</v>
+        <v>44966.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>1153.65</v>
+        <v>1166.1</v>
       </c>
       <c r="I17" t="n">
         <v>1165.636295300745</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="L17" t="n">
         <v>2.45</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>7.55</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1101</v>
+        <v>1089.4</v>
       </c>
       <c r="I18" t="n">
         <v>1094.534601672536</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.58</v>
+        <v>-6.58</v>
       </c>
       <c r="L18" t="n">
-        <v>6.01</v>
+        <v>7.45</v>
       </c>
       <c r="M18" t="n">
         <v>0.52</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>4.53</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1099.95</v>
+        <v>1127</v>
       </c>
       <c r="I19" t="n">
         <v>1121.885249513601</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.97</v>
+        <v>-3.45</v>
       </c>
       <c r="L19" t="n">
-        <v>1.91</v>
+        <v>3.54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.28</v>
+        <v>0.82</v>
       </c>
       <c r="N19" t="n">
         <v>2.51</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>5.59</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1146</v>
+        <v>1071.75</v>
       </c>
       <c r="I20" t="n">
         <v>1107.091398796878</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>1.69</v>
+        <v>-4.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.91</v>
+        <v>5.31</v>
       </c>
       <c r="M20" t="n">
-        <v>1.26</v>
+        <v>2.36</v>
       </c>
       <c r="N20" t="n">
-        <v>1.76</v>
+        <v>7.43</v>
       </c>
       <c r="O20" t="n">
         <v>2.46</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1069</v>
+        <v>1073.3</v>
       </c>
       <c r="I21" t="n">
         <v>1071.416519141549</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>0.26</v>
+        <v>-0.14</v>
       </c>
       <c r="L21" t="n">
         <v>4.41</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.71</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45051.38541666666</v>
+        <v>45051.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>1123.7</v>
+        <v>1082.75</v>
       </c>
       <c r="I22" t="n">
         <v>1103.300990625003</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>4.7</v>
+        <v>0.88</v>
       </c>
       <c r="L22" t="n">
         <v>6</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>7.29</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45055.55208333334</v>
+        <v>45056.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1141.65</v>
+        <v>1168.3</v>
       </c>
       <c r="I23" t="n">
         <v>1161.681380241258</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.44</v>
+        <v>-7.9</v>
       </c>
       <c r="L23" t="n">
-        <v>6.2</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.59</v>
+        <v>1.17</v>
       </c>
       <c r="N23" t="n">
         <v>4.21</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.47</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45093.55208333334</v>
+        <v>45096.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1310.9</v>
+        <v>1294.2</v>
       </c>
       <c r="I24" t="n">
         <v>1295.4056410491</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K24" t="n">
-        <v>12.21</v>
+        <v>10.78</v>
       </c>
       <c r="L24" t="n">
         <v>1.55</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>4.56</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45104.55208333334</v>
+        <v>45105.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1313.9</v>
+        <v>1332.95</v>
       </c>
       <c r="I25" t="n">
         <v>1326.961127974803</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.52</v>
+        <v>-2.99</v>
       </c>
       <c r="L25" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="N25" t="n">
         <v>2.99</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.74</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1379.7</v>
+        <v>1365.95</v>
       </c>
       <c r="I26" t="n">
         <v>1376.536717303379</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>3.51</v>
+        <v>2.48</v>
       </c>
       <c r="L26" t="n">
         <v>1.25</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>4.29</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45147.55208333334</v>
+        <v>45148.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1406</v>
+        <v>1417.8</v>
       </c>
       <c r="I27" t="n">
         <v>1415.524422330648</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.93</v>
+        <v>-3.8</v>
       </c>
       <c r="L27" t="n">
-        <v>4.03</v>
+        <v>4.68</v>
       </c>
       <c r="M27" t="n">
         <v>0.39</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,25 +2351,25 @@
         <v>3.98</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45155.55208333334</v>
+        <v>45156.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1376.25</v>
+        <v>1364.5</v>
       </c>
       <c r="I28" t="n">
         <v>1367.481710277093</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.93</v>
+        <v>-3.76</v>
       </c>
       <c r="L28" t="n">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="M28" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="N28" t="n">
         <v>2.43</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>4.12</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45161.55208333334</v>
+        <v>45162.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1399.15</v>
+        <v>1428.05</v>
       </c>
       <c r="I29" t="n">
         <v>1419.75836667709</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.54</v>
+        <v>-4.66</v>
       </c>
       <c r="L29" t="n">
-        <v>3.19</v>
+        <v>5.17</v>
       </c>
       <c r="M29" t="n">
-        <v>0.24</v>
+        <v>0.65</v>
       </c>
       <c r="N29" t="n">
         <v>2.03</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>4.2</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45168.55208333334</v>
+        <v>45169.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1392.5</v>
+        <v>1364.1</v>
       </c>
       <c r="I30" t="n">
         <v>1372.539026837606</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.49</v>
+        <v>-4.48</v>
       </c>
       <c r="L30" t="n">
-        <v>2.89</v>
+        <v>4.51</v>
       </c>
       <c r="M30" t="n">
         <v>0.05</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>5.37</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45176.38541666666</v>
+        <v>45176.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1407.3</v>
+        <v>1438</v>
       </c>
       <c r="I31" t="n">
         <v>1429.787425200189</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.17</v>
+        <v>-5.42</v>
       </c>
       <c r="L31" t="n">
-        <v>4.82</v>
+        <v>5.8</v>
       </c>
       <c r="M31" t="n">
         <v>0.63</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>4.97</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1434</v>
+        <v>1397</v>
       </c>
       <c r="I32" t="n">
         <v>1407.992051452562</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.28</v>
+        <v>-2.85</v>
       </c>
       <c r="L32" t="n">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="M32" t="n">
         <v>0.96</v>
       </c>
       <c r="N32" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="O32" t="n">
         <v>2.33</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>5.39</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45212.38541666666</v>
+        <v>45212.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1454</v>
+        <v>1459.05</v>
       </c>
       <c r="I33" t="n">
         <v>1458.397988847979</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.08</v>
+        <v>-4.44</v>
       </c>
       <c r="L33" t="n">
-        <v>4.29</v>
+        <v>4.96</v>
       </c>
       <c r="M33" t="n">
         <v>0.9399999999999999</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>4.25</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1640.35</v>
+        <v>1614.65</v>
       </c>
       <c r="I34" t="n">
         <v>1622.816263423142</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>96</v>
+        <v>96.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>12.43</v>
+        <v>10.66</v>
       </c>
       <c r="L34" t="n">
         <v>4.48</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>4.63</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45355.38541666666</v>
+        <v>45355.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1524.95</v>
+        <v>1531.55</v>
       </c>
       <c r="I35" t="n">
         <v>1528.756385356759</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>5.56</v>
+        <v>5.15</v>
       </c>
       <c r="L35" t="n">
         <v>1.55</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>5.24</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>1507.85</v>
+        <v>1495</v>
       </c>
       <c r="I36" t="n">
         <v>1499.061647478449</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.55</v>
+        <v>-2.39</v>
       </c>
       <c r="L36" t="n">
-        <v>1.71</v>
+        <v>2.39</v>
       </c>
       <c r="M36" t="n">
         <v>0.17</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>5.07</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45373.38541666666</v>
+        <v>45373.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1501.85</v>
+        <v>1518</v>
       </c>
       <c r="I37" t="n">
         <v>1515.123998524422</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.46</v>
+        <v>-1.54</v>
       </c>
       <c r="L37" t="n">
-        <v>1.07</v>
+        <v>1.7</v>
       </c>
       <c r="M37" t="n">
         <v>1.12</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.67</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1538.1</v>
+        <v>1498.25</v>
       </c>
       <c r="I38" t="n">
         <v>1504.778039638921</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K38" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="L38" t="n">
         <v>1.32</v>
       </c>
-      <c r="L38" t="n">
-        <v>1.2</v>
-      </c>
       <c r="M38" t="n">
-        <v>0.42</v>
+        <v>0.53</v>
       </c>
       <c r="N38" t="n">
-        <v>1.13</v>
+        <v>2.85</v>
       </c>
       <c r="O38" t="n">
         <v>2.29</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.47</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45436.55208333334</v>
+        <v>45439.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1443.55</v>
+        <v>1470.75</v>
       </c>
       <c r="I39" t="n">
         <v>1458.866827317705</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>3.65</v>
+        <v>1.84</v>
       </c>
       <c r="L39" t="n">
         <v>2.59</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>5.15</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1528.95</v>
+        <v>1413.2</v>
       </c>
       <c r="I40" t="n">
         <v>1451.027837801214</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K40" t="n">
-        <v>3.96</v>
+        <v>-3.91</v>
       </c>
       <c r="L40" t="n">
-        <v>2.15</v>
+        <v>7.29</v>
       </c>
       <c r="M40" t="n">
-        <v>0.37</v>
+        <v>1.24</v>
       </c>
       <c r="N40" t="n">
-        <v>0.8100000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="O40" t="n">
         <v>1.27</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.45</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45461.55208333334</v>
+        <v>45462.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1508.5</v>
+        <v>1532.55</v>
       </c>
       <c r="I41" t="n">
         <v>1532.287451381017</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.74</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>7.69</v>
+        <v>9.68</v>
       </c>
       <c r="M41" t="n">
         <v>1.03</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>4.82</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45471.55208333334</v>
+        <v>45474.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1464.2</v>
+        <v>1458.95</v>
       </c>
       <c r="I42" t="n">
         <v>1460.926516824143</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.46</v>
+        <v>-4.8</v>
       </c>
       <c r="L42" t="n">
-        <v>4.7</v>
+        <v>5.19</v>
       </c>
       <c r="M42" t="n">
         <v>1.16</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>4.51</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45504.55208333334</v>
+        <v>45505.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1428</v>
+        <v>1434.5</v>
       </c>
       <c r="I43" t="n">
         <v>1428.942925056917</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K43" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="L43" t="n">
         <v>0.6899999999999999</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>3.93</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45510.55208333334</v>
+        <v>45511.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1379.6</v>
+        <v>1346.45</v>
       </c>
       <c r="I44" t="n">
         <v>1378.111709579034</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>-3.83</v>
+        <v>-6.14</v>
       </c>
       <c r="L44" t="n">
-        <v>4.57</v>
+        <v>6.36</v>
       </c>
       <c r="M44" t="n">
         <v>1.21</v>
       </c>
       <c r="N44" t="n">
-        <v>1.28</v>
+        <v>2.35</v>
       </c>
       <c r="O44" t="n">
         <v>-0.7</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.16</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45531.55208333334</v>
+        <v>45532.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1380.05</v>
+        <v>1418.6</v>
       </c>
       <c r="I45" t="n">
         <v>1396.206450474622</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.5</v>
+        <v>-5.36</v>
       </c>
       <c r="L45" t="n">
-        <v>3.94</v>
+        <v>5.59</v>
       </c>
       <c r="M45" t="n">
         <v>1.41</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>4.68</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45559.55208333334</v>
+        <v>45560.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1447</v>
+        <v>1434.1</v>
       </c>
       <c r="I46" t="n">
         <v>1437.367402676302</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="L46" t="n">
         <v>2.54</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>4.58</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>970.4</v>
+        <v>985</v>
       </c>
       <c r="I47" t="n">
         <v>973.1385276431199</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>98.16666666666667</v>
+        <v>99</v>
       </c>
       <c r="K47" t="n">
-        <v>32.33</v>
+        <v>31.32</v>
       </c>
       <c r="L47" t="n">
         <v>3.27</v>
@@ -3120,7 +3683,7 @@
         <v>2.14</v>
       </c>
       <c r="N47" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="O47" t="n">
         <v>-0.41</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.41</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>981.7</v>
+        <v>943.85</v>
       </c>
       <c r="I48" t="n">
         <v>956.2817639789308</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.34</v>
+        <v>-4.18</v>
       </c>
       <c r="L48" t="n">
-        <v>2.21</v>
+        <v>4.53</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3</v>
+        <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2.61</v>
+        <v>4.37</v>
       </c>
       <c r="O48" t="n">
         <v>2.64</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>7.6</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>959.5</v>
+        <v>993.95</v>
       </c>
       <c r="I49" t="n">
         <v>982.1167625704334</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.66</v>
+        <v>-5.31</v>
       </c>
       <c r="L49" t="n">
-        <v>4.96</v>
+        <v>5.87</v>
       </c>
       <c r="M49" t="n">
         <v>1.34</v>
       </c>
       <c r="N49" t="n">
-        <v>2.28</v>
+        <v>3.72</v>
       </c>
       <c r="O49" t="n">
         <v>-4.37</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.85</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1040.7</v>
+        <v>983.5</v>
       </c>
       <c r="I50" t="n">
         <v>1017.779252350534</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K50" t="n">
-        <v>4.7</v>
+        <v>-1.05</v>
       </c>
       <c r="L50" t="n">
         <v>4.11</v>
@@ -3291,7 +3890,7 @@
         <v>1.83</v>
       </c>
       <c r="N50" t="n">
-        <v>2.68</v>
+        <v>6.57</v>
       </c>
       <c r="O50" t="n">
         <v>3.72</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.24</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45750.38541666666</v>
+        <v>45750.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>706.95</v>
+        <v>708.6</v>
       </c>
       <c r="I51" t="n">
         <v>708.5402112180174</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K51" t="n">
-        <v>28.12</v>
+        <v>27.95</v>
       </c>
       <c r="L51" t="n">
         <v>5.81</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.75</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45786.55208333334</v>
+        <v>45789.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>817.5</v>
+        <v>794.35</v>
       </c>
       <c r="I52" t="n">
         <v>797.3879360249192</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>36</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K52" t="n">
-        <v>15.37</v>
+        <v>12.1</v>
       </c>
       <c r="L52" t="n">
         <v>10.1</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.12</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45803.55208333334</v>
+        <v>45804.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>800.75</v>
+        <v>824.2</v>
       </c>
       <c r="I53" t="n">
         <v>820.2311195426089</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.76</v>
       </c>
       <c r="L53" t="n">
         <v>5.5</v>
@@ -3462,7 +4097,7 @@
         <v>2.14</v>
       </c>
       <c r="N53" t="n">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="O53" t="n">
         <v>-3.32</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.68</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45856.55208333334</v>
+        <v>45859.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>874</v>
+        <v>843.55</v>
       </c>
       <c r="I54" t="n">
         <v>845.8133417250713</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K54" t="n">
-        <v>6.04</v>
+        <v>2.35</v>
       </c>
       <c r="L54" t="n">
         <v>3.18</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.26</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45933.38541666666</v>
+        <v>45933.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>746.95</v>
+        <v>748</v>
       </c>
       <c r="I55" t="n">
         <v>747.0537905282786</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>74</v>
+        <v>74.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>11.45</v>
+        <v>11.33</v>
       </c>
       <c r="L55" t="n">
         <v>4.87</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.89</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46001.38541666666</v>
+        <v>46001.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>837.15</v>
+        <v>832</v>
       </c>
       <c r="I56" t="n">
         <v>834.4421105604476</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>67.83333333333333</v>
+        <v>68</v>
       </c>
       <c r="K56" t="n">
-        <v>11.92</v>
+        <v>11.23</v>
       </c>
       <c r="L56" t="n">
         <v>2.9</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.44</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46022.55208333334</v>
+        <v>46023.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>865.5</v>
+        <v>886.8</v>
       </c>
       <c r="I57" t="n">
         <v>868.4994244806662</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.03</v>
+        <v>-6.59</v>
       </c>
       <c r="L57" t="n">
-        <v>4.52</v>
+        <v>6.83</v>
       </c>
       <c r="M57" t="n">
         <v>0.74</v>
       </c>
       <c r="N57" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="O57" t="n">
         <v>-1.57</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.94</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46043.55208333334</v>
+        <v>46044.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>905.05</v>
+        <v>897.4</v>
       </c>
       <c r="I58" t="n">
         <v>900.2580870309284</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K58" t="n">
-        <v>2.06</v>
+        <v>1.2</v>
       </c>
       <c r="L58" t="n">
         <v>2.63</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>7.07</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46069.55208333334</v>
+        <v>46070.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>931.95</v>
+        <v>944.75</v>
       </c>
       <c r="I59" t="n">
         <v>934.9564100696857</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.85</v>
+        <v>-5.28</v>
       </c>
       <c r="L59" t="n">
         <v>6.93</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.8</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>915</v>
+        <v>872.25</v>
       </c>
       <c r="I60" t="n">
         <v>910.2177937519781</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.15</v>
+        <v>-7.67</v>
       </c>
       <c r="L60" t="n">
-        <v>3.47</v>
+        <v>7.81</v>
       </c>
       <c r="M60" t="n">
         <v>1.88</v>
       </c>
       <c r="N60" t="n">
-        <v>2.3</v>
+        <v>3.83</v>
       </c>
       <c r="O60" t="n">
         <v>1.23</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.23</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>782.1</v>
+        <v>831.4</v>
       </c>
       <c r="I61" t="n">
         <v>820.0685885734632</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K61" t="n">
-        <v>10.34</v>
+        <v>4.68</v>
       </c>
       <c r="L61" t="n">
         <v>4.04</v>
       </c>
       <c r="M61" t="n">
-        <v>1.58</v>
+        <v>3.82</v>
       </c>
       <c r="N61" t="n">
-        <v>4.24</v>
+        <v>6.89</v>
       </c>
       <c r="O61" t="n">
         <v>-3.83</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>921.1</v>
+        <v>895.95</v>
       </c>
       <c r="I62" t="n">
         <v>903.7529240825113</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K62" t="n">
-        <v>10.79</v>
+        <v>7.76</v>
       </c>
       <c r="L62" t="n">
         <v>3.69</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>7.4</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46168.38541666666</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>924.65</v>
+        <v>935</v>
       </c>
       <c r="I63" t="n">
         <v>934.6554410736932</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.2</v>
+        <v>-4.36</v>
       </c>
       <c r="L63" t="n">
-        <v>4.19</v>
+        <v>4.36</v>
       </c>
       <c r="M63" t="n">
         <v>1.1</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.02</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46175.55208333334</v>
+        <v>46176.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>915</v>
+        <v>893.8</v>
       </c>
       <c r="I64" t="n">
         <v>894.2490777954247</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.14</v>
+        <v>-4.41</v>
       </c>
       <c r="L64" t="n">
-        <v>4.76</v>
+        <v>5.45</v>
       </c>
       <c r="M64" t="n">
         <v>0.96</v>
       </c>
       <c r="N64" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="O64" t="n">
         <v>0.8100000000000001</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>5.65</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46191.38541666666</v>
+        <v>46191.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>935.9</v>
+        <v>939.95</v>
       </c>
       <c r="I65" t="n">
         <v>938.3620614311328</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.71</v>
+        <v>-5.16</v>
       </c>
       <c r="L65" t="n">
         <v>6.68</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>4.66</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46196.38541666666</v>
+        <v>46196.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>909.45</v>
+        <v>903</v>
       </c>
       <c r="I66" t="n">
         <v>904.9220443181304</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.24</v>
+        <v>-3.93</v>
       </c>
       <c r="L66" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="M66" t="n">
         <v>0.15</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>4.87</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>941.5</v>
+        <v>955.5</v>
       </c>
       <c r="I67" t="n">
         <v>946.9769092228746</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.26</v>
+        <v>-5.81</v>
       </c>
       <c r="L67" t="n">
-        <v>5.16</v>
+        <v>6.59</v>
       </c>
       <c r="M67" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N67" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="O67" t="n">
         <v>-1.72</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.99</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46225.55208333334</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1072</v>
+        <v>1001.3</v>
       </c>
       <c r="I68" t="n">
         <v>1019.820502118156</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K68" t="n">
-        <v>12.19</v>
+        <v>4.79</v>
       </c>
       <c r="L68" t="n">
         <v>1.4</v>
       </c>
       <c r="M68" t="n">
-        <v>0.91</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>2.08</v>
+        <v>6.3</v>
       </c>
       <c r="O68" t="n">
         <v>3.75</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>132</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7314,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.7</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7324,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7334,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98.2</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7344,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.7</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.5</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="11">
@@ -6569,7 +7404,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7414,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.49</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.47</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7434,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.33</v>
+        <v>31.32</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7444,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7454,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.79</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7464,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.9</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="21">
@@ -6649,7 +7484,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -6669,7 +7504,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
@@ -6689,7 +7524,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.87</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7534,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.51</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7544,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
